--- a/documents/human_resources.xlsx
+++ b/documents/human_resources.xlsx
@@ -516,7 +516,6 @@
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
         <v>95400</v>
       </c>
@@ -568,7 +567,6 @@
           <t>2018-06-27</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
         <v>110500</v>
       </c>
@@ -620,7 +618,6 @@
           <t>2023-07-03</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
         <v>85000</v>
       </c>
@@ -672,7 +669,6 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
         <v>68500</v>
       </c>
@@ -724,7 +720,6 @@
           <t>2023-09-03</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
         <v>78000</v>
       </c>
@@ -776,7 +771,6 @@
           <t>2018-11-24</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
         <v>84000</v>
       </c>
@@ -828,7 +822,6 @@
           <t>2021-01-15</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
         <v>79900</v>
       </c>
@@ -880,7 +873,6 @@
           <t>2023-10-27</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>84900</v>
       </c>
@@ -932,7 +924,6 @@
           <t>2022-08-24</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>124900</v>
       </c>
@@ -984,7 +975,6 @@
           <t>2018-01-20</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>122600</v>
       </c>
@@ -1036,7 +1026,6 @@
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
         <v>60800</v>
       </c>
@@ -1088,7 +1077,6 @@
           <t>2023-11-26</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
         <v>65100</v>
       </c>
@@ -1140,7 +1128,6 @@
           <t>2023-02-24</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
         <v>70500</v>
       </c>
@@ -1192,7 +1179,6 @@
           <t>2024-05-23</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
         <v>94500</v>
       </c>
@@ -1244,7 +1230,6 @@
           <t>2023-03-11</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
         <v>80500</v>
       </c>
@@ -1296,7 +1281,6 @@
           <t>2023-07-12</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
         <v>107100</v>
       </c>
@@ -1348,7 +1332,6 @@
           <t>2023-10-11</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
         <v>106100</v>
       </c>
@@ -1400,7 +1383,6 @@
           <t>2023-12-25</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
         <v>69700</v>
       </c>
@@ -1452,7 +1434,6 @@
           <t>2025-07-12</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="n">
         <v>69600</v>
       </c>
@@ -1504,7 +1485,6 @@
           <t>2022-08-25</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="n">
         <v>80600</v>
       </c>
@@ -1556,7 +1536,6 @@
           <t>2023-08-02</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="n">
         <v>73600</v>
       </c>
@@ -1608,7 +1587,6 @@
           <t>2021-10-13</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="n">
         <v>76500</v>
       </c>
@@ -1660,7 +1638,6 @@
           <t>2022-02-22</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
         <v>91300</v>
       </c>
@@ -1712,7 +1689,6 @@
           <t>2023-08-08</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="n">
         <v>67200</v>
       </c>
@@ -1764,7 +1740,6 @@
           <t>2022-12-17</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
       <c r="G26" t="n">
         <v>86300</v>
       </c>
@@ -1816,7 +1791,6 @@
           <t>2025-03-04</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
       <c r="G27" t="n">
         <v>84900</v>
       </c>
@@ -1868,7 +1842,6 @@
           <t>2022-06-25</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="n">
         <v>87400</v>
       </c>
@@ -1920,7 +1893,6 @@
           <t>2021-05-15</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="n">
         <v>90200</v>
       </c>
@@ -1972,7 +1944,6 @@
           <t>2023-11-20</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="n">
         <v>79800</v>
       </c>
@@ -2024,7 +1995,6 @@
           <t>2023-04-11</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
       <c r="G31" t="n">
         <v>80300</v>
       </c>
@@ -2076,7 +2046,6 @@
           <t>2023-10-26</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="n">
         <v>68300</v>
       </c>
@@ -2128,7 +2097,6 @@
           <t>2021-10-26</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="n">
         <v>115200</v>
       </c>
@@ -2180,7 +2148,6 @@
           <t>2021-02-09</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
         <v>66500</v>
       </c>
@@ -2232,7 +2199,6 @@
           <t>2022-08-20</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
       <c r="G35" t="n">
         <v>74100</v>
       </c>
@@ -2284,7 +2250,6 @@
           <t>2024-09-12</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
       <c r="G36" t="n">
         <v>91200</v>
       </c>
@@ -2336,7 +2301,6 @@
           <t>2022-10-28</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
       <c r="G37" t="n">
         <v>67700</v>
       </c>
@@ -2388,7 +2352,6 @@
           <t>2023-12-22</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
       <c r="G38" t="n">
         <v>70800</v>
       </c>
@@ -2440,7 +2403,6 @@
           <t>2022-05-12</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
       <c r="G39" t="n">
         <v>77400</v>
       </c>
@@ -2492,7 +2454,6 @@
           <t>2020-05-06</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
       <c r="G40" t="n">
         <v>91000</v>
       </c>
@@ -2544,7 +2505,6 @@
           <t>2025-03-08</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
         <v>65400</v>
       </c>
@@ -2596,7 +2556,6 @@
           <t>2019-01-11</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
         <v>91300</v>
       </c>
@@ -2648,7 +2607,6 @@
           <t>2021-10-27</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
         <v>75400</v>
       </c>
@@ -2700,7 +2658,6 @@
           <t>2022-08-22</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
         <v>105900</v>
       </c>
@@ -2752,7 +2709,6 @@
           <t>2022-07-06</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
         <v>108800</v>
       </c>
@@ -2804,7 +2760,6 @@
           <t>2022-01-07</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
         <v>87100</v>
       </c>
@@ -2856,7 +2811,6 @@
           <t>2022-08-13</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
       <c r="G47" t="n">
         <v>112100</v>
       </c>
@@ -2908,7 +2862,6 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
         <v>73300</v>
       </c>
@@ -2960,7 +2913,6 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
         <v>94400</v>
       </c>
@@ -3012,7 +2964,6 @@
           <t>2021-06-02</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
         <v>116800</v>
       </c>
@@ -3064,7 +3015,6 @@
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
         <v>94700</v>
       </c>
@@ -3116,7 +3066,6 @@
           <t>2018-03-07</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
         <v>111400</v>
       </c>
@@ -3168,7 +3117,6 @@
           <t>2025-10-18</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
         <v>80400</v>
       </c>
@@ -3220,7 +3168,6 @@
           <t>2024-04-08</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
         <v>78900</v>
       </c>
@@ -3272,7 +3219,6 @@
           <t>2023-04-08</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
         <v>85700</v>
       </c>
@@ -3324,7 +3270,6 @@
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
         <v>80100</v>
       </c>
@@ -3376,7 +3321,6 @@
           <t>2022-05-19</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
         <v>104900</v>
       </c>
@@ -3428,7 +3372,6 @@
           <t>2021-07-28</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
         <v>99800</v>
       </c>
@@ -3480,7 +3423,6 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
         <v>64700</v>
       </c>
@@ -3532,7 +3474,6 @@
           <t>2021-06-23</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
         <v>84900</v>
       </c>
@@ -3584,7 +3525,6 @@
           <t>2023-05-07</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
         <v>104300</v>
       </c>
@@ -3636,7 +3576,6 @@
           <t>2022-11-28</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
         <v>77300</v>
       </c>
@@ -3688,7 +3627,6 @@
           <t>2025-10-18</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
       <c r="G63" t="n">
         <v>70600</v>
       </c>
@@ -3740,7 +3678,6 @@
           <t>2023-06-27</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
         <v>76800</v>
       </c>
@@ -3792,7 +3729,6 @@
           <t>2018-08-08</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
       <c r="G65" t="n">
         <v>138000</v>
       </c>
@@ -3844,7 +3780,6 @@
           <t>2024-11-02</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
       <c r="G66" t="n">
         <v>71300</v>
       </c>
@@ -3896,7 +3831,6 @@
           <t>2024-09-09</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
       <c r="G67" t="n">
         <v>119600</v>
       </c>
@@ -3948,7 +3882,6 @@
           <t>2023-07-24</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
       <c r="G68" t="n">
         <v>69700</v>
       </c>
@@ -4000,7 +3933,6 @@
           <t>2023-01-26</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
       <c r="G69" t="n">
         <v>74600</v>
       </c>
@@ -4052,7 +3984,6 @@
           <t>2021-07-05</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
       <c r="G70" t="n">
         <v>136700</v>
       </c>
@@ -4104,7 +4035,6 @@
           <t>2025-10-20</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
       <c r="G71" t="n">
         <v>69200</v>
       </c>
@@ -4156,7 +4086,6 @@
           <t>2021-09-25</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="n">
         <v>114300</v>
       </c>
@@ -4208,7 +4137,6 @@
           <t>2019-03-06</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
       <c r="G73" t="n">
         <v>95800</v>
       </c>
@@ -4260,7 +4188,6 @@
           <t>2023-05-19</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
       <c r="G74" t="n">
         <v>78500</v>
       </c>
@@ -4312,7 +4239,6 @@
           <t>2022-10-14</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
       <c r="G75" t="n">
         <v>77500</v>
       </c>
@@ -4364,7 +4290,6 @@
           <t>2023-11-19</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
       <c r="G76" t="n">
         <v>62400</v>
       </c>
@@ -4416,7 +4341,6 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
       <c r="G77" t="n">
         <v>97900</v>
       </c>
@@ -4468,7 +4392,6 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
       <c r="G78" t="n">
         <v>110600</v>
       </c>
@@ -4520,7 +4443,6 @@
           <t>2025-07-02</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
       <c r="G79" t="n">
         <v>74200</v>
       </c>
@@ -4572,7 +4494,6 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
       <c r="G80" t="n">
         <v>94200</v>
       </c>
@@ -4624,7 +4545,6 @@
           <t>2022-03-01</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
       <c r="G81" t="n">
         <v>82700</v>
       </c>
@@ -4676,7 +4596,6 @@
           <t>2024-12-13</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="n">
         <v>68800</v>
       </c>
@@ -4728,7 +4647,6 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
       <c r="G83" t="n">
         <v>64200</v>
       </c>
@@ -4780,7 +4698,6 @@
           <t>2024-05-23</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
       <c r="G84" t="n">
         <v>90300</v>
       </c>
@@ -4832,7 +4749,6 @@
           <t>2024-06-16</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
       <c r="G85" t="n">
         <v>83200</v>
       </c>
@@ -4884,7 +4800,6 @@
           <t>2026-01-04</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
         <v>82500</v>
       </c>
@@ -4936,7 +4851,6 @@
           <t>2023-09-06</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
       <c r="G87" t="n">
         <v>96300</v>
       </c>
@@ -4988,7 +4902,6 @@
           <t>2019-02-05</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
       <c r="G88" t="n">
         <v>91600</v>
       </c>
@@ -5040,7 +4953,6 @@
           <t>2024-10-11</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
       <c r="G89" t="n">
         <v>105700</v>
       </c>
@@ -5092,7 +5004,6 @@
           <t>2020-05-13</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
       <c r="G90" t="n">
         <v>105300</v>
       </c>
@@ -5144,7 +5055,6 @@
           <t>2022-09-03</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
       <c r="G91" t="n">
         <v>95500</v>
       </c>
@@ -5196,7 +5106,6 @@
           <t>2022-10-15</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
         <v>97500</v>
       </c>
@@ -5248,7 +5157,6 @@
           <t>2025-01-24</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
       <c r="G93" t="n">
         <v>82700</v>
       </c>
@@ -5300,7 +5208,6 @@
           <t>2021-09-25</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
       <c r="G94" t="n">
         <v>90800</v>
       </c>
@@ -5352,7 +5259,6 @@
           <t>2021-11-02</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
         <v>95900</v>
       </c>
@@ -5404,7 +5310,6 @@
           <t>2023-05-21</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
         <v>80000</v>
       </c>
@@ -5456,7 +5361,6 @@
           <t>2021-03-22</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
         <v>90800</v>
       </c>
@@ -5508,7 +5412,6 @@
           <t>2024-03-12</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
         <v>74100</v>
       </c>
@@ -5560,7 +5463,6 @@
           <t>2019-07-10</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
         <v>84900</v>
       </c>
@@ -5612,7 +5514,6 @@
           <t>2022-01-24</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
         <v>68000</v>
       </c>
@@ -5664,7 +5565,6 @@
           <t>2024-01-06</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
         <v>87600</v>
       </c>
@@ -5716,7 +5616,6 @@
           <t>2022-12-10</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
         <v>107500</v>
       </c>
@@ -5768,7 +5667,6 @@
           <t>2024-03-07</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
         <v>76400</v>
       </c>
@@ -5820,7 +5718,6 @@
           <t>2023-03-17</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
         <v>87600</v>
       </c>
@@ -5872,7 +5769,6 @@
           <t>2023-12-07</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
         <v>71900</v>
       </c>
@@ -5990,7 +5886,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -6102,7 +5998,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -6158,7 +6054,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -6438,7 +6334,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -6606,7 +6502,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -6662,7 +6558,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -6830,7 +6726,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -6932,7 +6828,6 @@
           <t>2022-11-03</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
       <c r="G124" t="n">
         <v>85200</v>
       </c>
@@ -7274,7 +7169,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -7432,7 +7327,6 @@
           <t>2023-08-18</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
       <c r="G133" t="n">
         <v>96300</v>
       </c>
@@ -7774,7 +7668,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -7830,7 +7724,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I140" t="n">
@@ -7886,7 +7780,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -8278,7 +8172,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -8726,7 +8620,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I156" t="n">
@@ -9174,7 +9068,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I164" t="n">
@@ -9230,7 +9124,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I165" t="n">
@@ -9286,7 +9180,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -9454,7 +9348,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I169" t="n">
@@ -9612,7 +9506,6 @@
           <t>2024-03-08</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr"/>
       <c r="G172" t="n">
         <v>59400</v>
       </c>
@@ -9674,7 +9567,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I173" t="n">
@@ -9720,7 +9613,6 @@
           <t>2022-11-09</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
       <c r="G174" t="n">
         <v>97400</v>
       </c>
@@ -9782,7 +9674,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -9838,7 +9730,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I176" t="n">
@@ -9894,7 +9786,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I177" t="n">
@@ -9996,7 +9888,6 @@
           <t>2024-11-28</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr"/>
       <c r="G179" t="n">
         <v>90100</v>
       </c>
@@ -10170,7 +10061,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I182" t="n">
@@ -10730,7 +10621,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I192" t="n">
@@ -10954,7 +10845,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -11066,7 +10957,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I198" t="n">
@@ -11122,7 +11013,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I199" t="n">
@@ -11290,7 +11181,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I202" t="n">
@@ -11346,7 +11237,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I203" t="n">
@@ -11402,7 +11293,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I204" t="n">
@@ -11570,7 +11461,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Resigned</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I207" t="n">

--- a/documents/human_resources.xlsx
+++ b/documents/human_resources.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:L212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,12 +567,17 @@
           <t>2018-06-27</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
       <c r="G3" t="n">
         <v>110500</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -720,12 +725,17 @@
           <t>2023-09-03</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
       <c r="G6" t="n">
         <v>78000</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1179,12 +1189,17 @@
           <t>2024-05-23</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
       <c r="G15" t="n">
         <v>94500</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1434,12 +1449,17 @@
           <t>2025-07-12</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
       <c r="G20" t="n">
         <v>69600</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1791,12 +1811,17 @@
           <t>2025-03-04</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
       <c r="G27" t="n">
         <v>84900</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2199,12 +2224,17 @@
           <t>2022-08-20</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="G35" t="n">
         <v>74100</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2352,12 +2382,17 @@
           <t>2023-12-22</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
       <c r="G38" t="n">
         <v>70800</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2505,12 +2540,17 @@
           <t>2025-03-08</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="G41" t="n">
         <v>65400</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2607,12 +2647,17 @@
           <t>2021-10-27</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="G43" t="n">
         <v>75400</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2658,12 +2703,17 @@
           <t>2022-08-22</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
       <c r="G44" t="n">
         <v>105900</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2709,12 +2759,17 @@
           <t>2022-07-06</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
       <c r="G45" t="n">
         <v>108800</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3015,12 +3070,17 @@
           <t>2026-02-27</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
       <c r="G51" t="n">
         <v>94700</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3168,12 +3228,17 @@
           <t>2024-04-08</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
       <c r="G54" t="n">
         <v>78900</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3831,12 +3896,17 @@
           <t>2024-09-09</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
       <c r="G67" t="n">
         <v>119600</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -3984,12 +4054,17 @@
           <t>2021-07-05</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
       <c r="G70" t="n">
         <v>136700</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4137,12 +4212,17 @@
           <t>2019-03-06</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
       <c r="G73" t="n">
         <v>95800</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4545,12 +4625,17 @@
           <t>2022-03-01</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
       <c r="G81" t="n">
         <v>82700</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -4749,12 +4834,17 @@
           <t>2024-06-16</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
       <c r="G85" t="n">
         <v>83200</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -4851,12 +4941,17 @@
           <t>2023-09-06</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
       <c r="G87" t="n">
         <v>96300</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -4902,12 +4997,17 @@
           <t>2019-02-05</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
       <c r="G88" t="n">
         <v>91600</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -4953,12 +5053,17 @@
           <t>2024-10-11</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
       <c r="G89" t="n">
         <v>105700</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -5106,12 +5211,17 @@
           <t>2022-10-15</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
       <c r="G92" t="n">
         <v>97500</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -5259,12 +5369,17 @@
           <t>2021-11-02</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
       <c r="G95" t="n">
         <v>95900</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Retired</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -5514,12 +5629,17 @@
           <t>2022-01-24</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="G100" t="n">
         <v>68000</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Terminated</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -5667,12 +5787,17 @@
           <t>2024-03-07</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
       <c r="G103" t="n">
         <v>76400</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Resigned</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -11534,6 +11659,210 @@
       <c r="L208" t="inlineStr">
         <is>
           <t>Black</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Kelly Moreno</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>1983-06-02</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Recruiter</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G209" t="n">
+        <v>98400</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>3</v>
+      </c>
+      <c r="J209" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Jennifer Nelson</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2001-03-06</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>HR Business Partner</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>74500</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>1</v>
+      </c>
+      <c r="J210" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Kayla Nelson</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>1985-06-11</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>HR Coordinator</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>57000</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Nicole Simmons</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>1978-12-18</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Human Resources</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>HR Business Partner</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>81000</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>White</t>
         </is>
       </c>
     </row>
